--- a/law/hi-bharatiya-adhiniyam-sandarbh_HI.xlsx
+++ b/law/hi-bharatiya-adhiniyam-sandarbh_HI.xlsx
@@ -11,165 +11,447 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>नाम</t>
   </si>
   <si>
-    <t>अंग्रेज़ी नाम</t>
-  </si>
-  <si>
-    <t>स्रोत का अंग्रेज़ी विवरण</t>
-  </si>
-  <si>
-    <t>स्रोत में दर्ज अधिकार क्षेत्र</t>
-  </si>
-  <si>
-    <t>वर्गीकरण</t>
+    <t>मूल विवरण</t>
   </si>
   <si>
     <t>स्रोत लिंक</t>
   </si>
   <si>
-    <t>उपभोक्ता संरक्षण अधिनियम, 2019</t>
-  </si>
-  <si>
-    <t>Consumer Protection Act, 2019</t>
-  </si>
-  <si>
-    <t>Indian Government Law</t>
-  </si>
-  <si>
-    <t>भारत</t>
-  </si>
-  <si>
-    <t>भारतीय संसद का अधिनियम</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q66809767</t>
-  </si>
-  <si>
-    <t>पर्यावरण संरक्षण अधिनियम, 1986</t>
-  </si>
-  <si>
-    <t>Environment (Protection) Act, 1986</t>
-  </si>
-  <si>
-    <t>Act of the Parliament of India</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q12437271</t>
-  </si>
-  <si>
-    <t>हिन्दू विवाह अधिनियम, 1955</t>
-  </si>
-  <si>
-    <t>Hindu Marriage Act, 1955</t>
-  </si>
-  <si>
-    <t>act by Indian parliament governing Marriages &amp; Divorce applicable to Hindus, Buddhists, Jains, and Sikhs</t>
-  </si>
-  <si>
-    <t>भारतीय संसद का अधिनियम; विवाह कानून</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q5766344</t>
-  </si>
-  <si>
-    <t>भारतीय संविदा अधिनियम, 1872</t>
-  </si>
-  <si>
-    <t>Indian Contract Act, 1872</t>
-  </si>
-  <si>
-    <t>Act of Imperial Legislative Council of India</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>इंपीरियल विधान परिषद का अधिनियम</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3595898</t>
+    <t>आतंकवाद निरोधी अधिनियम, २००२</t>
+  </si>
+  <si>
+    <t>अत्याचार विरोधी अधिनियम, २००२ - देश में आतंकवाद पर अकुंश लगाने के उद्देश्य से २ अप्रैल २००२ को टाडा के स्थान पर एक नया आतंकवाद निरोधी अधिनियम पोटा लागू किया गया। संसद के दोनों सदनों के संयुक्त अधिवेशन में २६ मार्च २००२ पारित होने के बाद २ अप्रैल २००२ को राष्ट्रपति के अनुमोदन के साथ ही यह विधेयक एक अधिनियम पोटा के रूप में आस्तित्व में आया। भारतीय संविधान के अनुच्छेद 22 के खंड-3,4,5 तथा 6 में निवारक निरोध तत्सम्बन्धी प्रावधानों का उल्लेख है । निवारक निरोध कानून के अंतर्गत किसी व्यक्ति को अपराध के पूर्व ही गिरफ्तार किया जाता है । निवारक निरोध का उद्धेश्य व्यक्ति को अपराध के लिए दंड देना नहीं,वरन उसे अपराध करने से रोकना है । वस्तुतः यह निवारक निरोध राज्य की सुरक्षा, लोक व्यवस्था बनाये रखने या भारत की सुरक्षा संबंधी कारणों से हो सकता है । जब किसी व्यक्ति को निवारक निरोध के अधीन गिरफ्तार किया जाता है, तब- 1) सरकार ऐसे व्यक्ति को केवल 3 महीने तक अभिरक्षा में निरुद्ध कर सकती है। यदि गिरफ्तार व्यक्ति को 3 माह से अधिक के लिए निरुद्ध करना होता है तो इसके लिए सलाहकार बोर्ड का प्रतिवेदन प्राप्त करना पड़ता है । 2) इस प्रकार निरुद्ध व्यक्ति को यथाशीघ्र निरोध के आधार पर सूचित किये जायेंगे,किन्तु जिन तथ्यो को निरस्त करना लोकहित के विरुद्ध समझा जाएगा उन्हें प्रकट करना आवश्यक नहीं है । 3) निरुद्ध व्यक्ति को निरोध आदेश के विरुद्ध अभ्यावेदन करने के लिए शीघ्रातिशीघ्र अवसर दिया जाना चाहिए । निवारक निरोध से सम्बंधित अभी तक बनाई गई विधियाँ १) निवारक निरोध अधिनियम,1950: भारत की संसद ने 26 फरवरी1950 को पहला निवारक निरोध अधिनियम पारित किया था । इसका उद्देश्य राष्ट्र विरोधी तत्वों को भारत की प्रतिरक्षा के प्रतिकूल कार्य करने से रोकना था। इसे 1 अप्रैल, 1951 को समाप्त हो जाना था , किन्तु समय-समय पर इसका जीवनकाल बढ़ाया जाता रहा । अंततः यह 31 दिसंबर, 1971 को समाप्त हुआ । २) आंतरिक सुरक्षा व्यवस्था अधिनियम , 1971-(MISA): 44वे संवैधानिक संशोधन(1979) इसके प्रतिकूल था और इस कारण अप्रैल, 1979 ई में यह समाप्त हो गया । ३) आतंकवादी एवं विध्वंशकारी गतिविधियां निरोधक कानून (टाडा) : निवारक निरोध व्यवस्था के अंतर्गत अबतक जो कानून बने उनमे यह सबसे प्रभावी और सर्वाधिक कठोर कानून था । 23 मई,1995 को इसे समाप्त कर दिया गया ४) पोटो (prevention of terrorism ordinance,2001): इसे 25 अक्टूबर,2001 को लागू किया गया था । 'पोटो' टाडा का ही एक रूप है। इसके अंतर्गत कुल 23 आतंकवादी गुटों को प्रतिबंधित किया गया है । आतंकवादीऔर आतंकवादियों से संबंधित सूचना को छिपाने वालो को भी दंडित करने का प्रवधान किया गया है । पुलिस शक के आधार पर किसी को भी गिरफ्तार कर सकती है ,किन्तु बिना आरोप-पत्र के तीन माह से अधिक हिरासत में नहीं रख सकती । पोटा के अंतर्गत गिरफ्तार व्यक्ति हाई कोर्ट या सुप्रीम कोर्ट में अपील कर सकता है, लेकिन यह अपील भी गिरफ्तारी के तीन माह बाद ही हो सकती है । पोटो 28 मार्च 2002 को अधिनियम बनने के बाद पोटा हो गया । इसे 21 सितम्बर,2004 को अध्यादेश के द्वारा समाप्त कर दिया गया ।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95%E0%A4%B5%E0%A4%BE%E0%A4%A6_%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A8%E0%A5%A6%E0%A5%A6%E0%A5%A8&amp;oldid=6484247</t>
+  </si>
+  <si>
+    <t>गर्भ का चिकित्सकीय समापन अधिनियम, 1971</t>
+  </si>
+  <si>
+    <t>गर्भ का चिकित्सकीय समापन अधिनियम, 1971 (Medical Termination of Pregnancy Act, 1971) भारत सरकार का एक अधिनियम है जो कुछ विशेष परिस्थितियों में अनचाहे गर्भ से छुटकारा पाने की अनुमति देता है। यह अधिनियम सन् 1971 में बनाया गया था तथा वर्ष 2002 में कानून में आवश्‍यक संशोधन किये गये। इस कानून के अन्‍तर्गत महिलायें कुछ विशेष परिस्थितियों में सरकारी अस्‍पताल में या सरकार की ओर से अधिकृत किसी से भी चिकित्‍सा केन्‍द्र में अधिकृत व प्रशिक्षित डॉक्‍टर द्वारा गर्भपात करा सकती है। गर्भ-समापन के लिये घर के किसी सदस्‍य की लिखित इजाजत की जरूरत नहीं होती है, लेकिन 18 वर्ष से कम आयु की महिलाओं अथवा जिसने 18 वर्ष की आयु प्राप्‍त कर ली हो, लेकिन जो पागल हो, को माता-पिता या पति (यदि कोई नाबालिक लडकी की शादी हो गई हो) की लिखित इजाजत की जरूरत होती है। 18 वर्ष या उससे अधिक उम्र की महिलाओं का केवल स्‍वयं की लिखित स्‍वीकृति ही देनी जरूरी है|</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AD_%E0%A4%95%E0%A4%BE_%E0%A4%9A%E0%A4%BF%E0%A4%95%E0%A4%BF%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%95%E0%A5%80%E0%A4%AF_%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%AA%E0%A4%A8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1971&amp;oldid=6195409</t>
+  </si>
+  <si>
+    <t>धन-शोधन निवारण अधिनियम, 2002</t>
+  </si>
+  <si>
+    <t>धन-शोधन निवारण अधिनियम, २००२ भारत के संसद द्वारा पारित एक अधिनियम है जिसका उद्देश्य काले धन को सफेद करने से रोकना है। इसमें धन-शोधन से प्राप्त धन को राज्यसात (ज़ब्त) करने का प्रावधान है। यह अधिनियम 1 जुलाई, 2005 से प्रभावी हुआ। यह कानून गैर जमानती है इसके तहत दोषी को जमानत नहीं दी जा सकती है</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A7%E0%A4%A8-%E0%A4%B6%E0%A5%8B%E0%A4%A7%E0%A4%A8_%E0%A4%A8%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%A3_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_2002&amp;oldid=6250644</t>
+  </si>
+  <si>
+    <t>न्यूनतम मजदूरी अधिनियम, १९४८</t>
+  </si>
+  <si>
+    <t>न्यूनतम मजदूरी अधिनियम, 1948 (Minimum Wages Act, 1948) भारत की संसद द्वारा पारित एक श्रम कानून है जो कुशल तथा अकुशल श्रमिकों को दी जाने वाली मजदूरी का निर्धारण करता है। यह अधिनियम सरकार को विनिर्दिष्ट रोजगारों में कार्य कर रहे कर्मचारियों के लिए न्यूनतम मजदूरी निर्धारित करने के लिए प्राधिकृत करता है। इसमें उपयुक्त अन्तरालों और अधिकतम पाँच वर्षो के अन्तराल पर पहले से निर्धारित न्यूनतम मजदूरियों की समीक्षा करने तथा उनमें संशोधन करने का प्रावधान है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%A8%E0%A4%A4%E0%A4%AE_%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AA%E0%A5%AE&amp;oldid=6196282</t>
+  </si>
+  <si>
+    <t>रियल एस्टेट (विनियमन और विकास) अधिनियम, 2016</t>
+  </si>
+  <si>
+    <t>रियल एस्टेट (विनियमन और विकास) अधिनियम, 2016 (The Real Estate (Regulation and Development) Act, 2016) भारतीय संसद का एक अधिनियम है जो घरेलू खरीददारों की रक्षा करने के साथ-साथ स्थावर सम्पदा (रियल एस्टेट) में पूँजी निवेश को बढ़ावा देने में मदद करता है। यह अधिनियम राज्यसभा में १० मार्च २०१६ को तथा लोकसभा में १५ मार्च २०१६ को पारित हुआ था। इसकी ९२ में से ६९ धाराओं को लागू करते हुए इस अधिनियम को ०१ मई २०१६ से लागू कर दिया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A4%B2_%E0%A4%8F%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F_(%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE%E0%A4%A8_%E0%A4%94%E0%A4%B0_%E0%A4%B5%E0%A4%BF%E0%A4%95%E0%A4%BE%E0%A4%B8)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_2016&amp;oldid=5652717</t>
+  </si>
+  <si>
+    <t>समिति रजिस्ट्रीकरण अधिनियम, १८६०</t>
+  </si>
+  <si>
+    <t>समिति रजिस्ट्रीकरण अधिनियम, १८६० (Societies Registration Act, 1860) भारत का एक अधिनियम है जो उन संस्थाओं की रजिस्ट्री करता है जो प्रायः समाज के हित के लिए कार्य करतीं हैं, जैसे शिक्षा, स्वास्थ्य, रोजगार आदि के क्षेत्र में कार्यरत समितियाँ। सोसाइटीज रजिस्ट्रेशन एक्ट, 1860 एक केन्द्रीय अधिनियम है तथा इस एक्ट के अन्तर्गत विभिन्न प्रकार की चैरिटेबल एवं अव्यवसायिक संस्थाएं पंजीकृत की जाती हैं। यह एक्ट पूरे भारतवर्ष में समान रूप से लागू है तथा इसमें समय-समय पर राज्यों द्वारा अपनी आवश्यकतानुसार संशोधन आदि किया जाता है। प्रत्येक राज्य की नियमावली भी अलग-अलग है। इस अधिनियम के अन्तर्गत वैज्ञानिक शैक्षणिक, धर्मार्थ एवं कल्याणार्थ हेतु निर्मित समितियों के पंजीकरण एवं प्रत्येक पांच वर्ष बाद पंजीकृत समितियों के नवीनीकरण का कार्य किया जाता है। संस्थाओं की प्रबन्ध समिति की वार्षिक सूची के पंजीकरण तथा संस्थाओं द्वारा अपने पंजीकृत उद्देश्यों या पंजीकृत विधान में आवश्यकतानुसार परिवर्तन, नाम में परिवर्तन की कार्यवाही प्रस्तुत किये जाने पर सोसाइटी रजिस्ट्रेशन ऐक्ट के सुसंगत नियमों के अन्तर्गत पंजीकरण का कार्य किया जाता है। संस्थाओं के द्वारा वित्तीय अनियमितताओं की शिकायत प्राप्त होने पर संस्था के लेखों की जांच एवं संस्था के कार्यकलापों का निरीक्षण भी किया जाता है। अधिनियम की धारा 4 (1) के परन्तुक के अन्तर्गत यदि चुनावोपरान्त पिछली कमेटी के पदाधिकारी या कार्यकारिणी सदस्य आपत्ति प्रस्तुत करते हैं तो रजिस्ट्रार द्वारा आपत्तियां आमन्त्रित करके उस पर सो0रजि0ऐक्ट के सुसंगत नियमों के अन्तर्गत आदेश पारित किये जाते हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%AE%E0%A4%BF%E0%A4%A4%E0%A4%BF_%E0%A4%B0%E0%A4%9C%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%95%E0%A4%B0%E0%A4%A3_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AE%E0%A5%AC%E0%A5%A6&amp;oldid=6192422</t>
+  </si>
+  <si>
+    <t>हिन्दू विवाह अधिनियम</t>
+  </si>
+  <si>
+    <t>हिन्दू विवाह अधिनियम भारत की संसद द्वारा सन् 1955 में पारित एक विधि है। इसी कालावधि में तीन अन्य महत्वपूर्ण विधियाँ पारित हुईं : हिन्दू उत्तराधिका अधिनियम (1956) , हिन्दू अप्राप्तवयता एवं संरक्षकता अधिनियम (1956) और हिन्दू दत्तक तथा भरण-पोषण अधिनियम (1956) । ये सभी नियम हिन्दुओं के वैधिक परम्पराओं को आधुनिक बनाने के ध्येय से लागू किए गये थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B9%E0%A4%BF%E0%A4%A8%E0%A5%8D%E0%A4%A6%E0%A5%82_%E0%A4%B5%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B9_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=6521945</t>
+  </si>
+  <si>
+    <t>सेबी अधिनियम 1992</t>
+  </si>
+  <si>
+    <t>दिल्ली बाजार की बदलती जरूरतों और प्रतिभूति बाजार में होने वाले विकास के प्रति प्रतिक्रिया व्यक्त करने की आवश्यकताओं को पूरा करने के लिए 1995, 1999 और 2002 में भारतीय प्रतिभूति एवं विनिमय बोर्ड अधिनियम 1992 (सिक्यूरिटीज एण्ड एक्सचेंज बोर्ड ऑफ इंडिया एक्ट 1992/सेबी अधिनियम) को संशोधित किया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A5%87%E0%A4%AC%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_1992&amp;oldid=5796213</t>
+  </si>
+  <si>
+    <t>अनुसूचित जाति एवं अनुसूचित जनजाति (अत्याचार निरोधक) अधिनियम, 1989</t>
+  </si>
+  <si>
+    <t>भारत में अनुसूचित जाति एवं अनुसूचित जनजाति के व्यक्तियों पर अत्याचार या उत्पीडन को रोकने के लिये अनुसूचित जाति एवं अनुसूचित जनजाति (अत्याचार निरोधक) अधिनियम (The Scheduled Castes and Tribes (Prevention of Atrocities) Act, 1989) भारतीय संसद द्वारा पारित किया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%BF%E0%A4%A4_%E0%A4%9C%E0%A4%BE%E0%A4%A4%E0%A4%BF_%E0%A4%8F%E0%A4%B5%E0%A4%82_%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%BF%E0%A4%A4_%E0%A4%9C%E0%A4%A8%E0%A4%9C%E0%A4%BE%E0%A4%A4%E0%A4%BF_(%E0%A4%85%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0_%E0%A4%A8%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7%E0%A4%95)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1989&amp;oldid=6624687</t>
+  </si>
+  <si>
+    <t>आतंकवादी तथा विघटनकारी क्रियाकलाप (निवारण) अधिनियम, १९८७</t>
+  </si>
+  <si>
+    <t>आतंकवादी तथा विघटनकारी क्रियाकलाप (निवारण) अधिनियम, १९८७ | इसे टाडा के नाम से जाना जाता हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95%E0%A4%B5%E0%A4%BE%E0%A4%A6%E0%A5%80_%E0%A4%A4%E0%A4%A5%E0%A4%BE_%E0%A4%B5%E0%A4%BF%E0%A4%98%E0%A4%9F%E0%A4%A8%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%80_%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A4%BE%E0%A4%95%E0%A4%B2%E0%A4%BE%E0%A4%AA_(%E0%A4%A8%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%A3)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AE%E0%A5%AD&amp;oldid=5655982</t>
+  </si>
+  <si>
+    <t>आवश्यक वस्तु अधिनियम</t>
+  </si>
+  <si>
+    <t>आवश्यक वस्‍तु अधिनियम, 1955 को उपभोक्‍ता ओं को अनिवार्य वस्‍तुओं की सहजता से उपलब्‍धता सुनिश्चित कराने तथा कपटी व्‍यापारियों के शोषण से उनकी रक्षा के लिए बनाया गया है। अधिनियम में उन वस्‍तुओं के उत्‍पादन वितरण और मूल्‍य निर्धारण को विनियमित एवं नियंत्रित करने की व्‍यवस्‍था की गई है, जिनकी आपूर्ति बनाए रखने या बढ़ाने तथा उनका समान वितरण प्राप्‍त करने और उचित मूल्‍य पर उनकी उपलब्‍धता के लिए अनिवार्य घोषित किया गया है। अधिनियम के तहत अधिकांश शक्तियां राज्‍य सरकारों को दी गई हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%B5%E0%A4%B6%E0%A5%8D%E0%A4%AF%E0%A4%95_%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%81_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=5893811</t>
+  </si>
+  <si>
+    <t>आवश्यक सेवा संरक्षण अधिनियम</t>
+  </si>
+  <si>
+    <t>आवश्‍यक सेवा अनुरक्षण कानून ( एस्‍मा ) हड़ताल को रोकने हेतु एस्‍मा लगाया जाता है। एस्‍मा लागू करने से पूर्व इससे प्रभावित होने वाले कर्मचारियों को किसी समाचार पत्र या अन्‍य माध्‍यम से सूचित किया जाता है। एस्‍मा का नियम अधिकतम ६ माह के लिए लगाया जा सकता है। एस्‍मा लागू होने के उपरान्‍त यदि कर्मचारी हड़ताल पर जाता है तो वह अवैध‍ एवं दण्‍डनीय है। क्रिमिनल प्रोसीजर १८९८ (५ ऑफ १८९८) के अन्‍तर्गत एस्‍मा लागू होने के उपरान्‍त इस आदेश से सम्‍बन्‍धि किसी भी कर्मचारी को बिना किसी वारन्‍ट के गिरफतार किया जा सकता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%B5%E0%A4%B6%E0%A5%8D%E0%A4%AF%E0%A4%95_%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE_%E0%A4%B8%E0%A4%82%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=6195430</t>
+  </si>
+  <si>
+    <t>उत्तर प्रदेश पुनर्गठन अधिनियम, 2000</t>
+  </si>
+  <si>
+    <t>उत्तर प्रदेश पुनर्गठन अधिनियम, 2000 भारत की संसद द्वारा पारित एक अधिनियम है, जिसके माध्यम से उत्तर प्रदेश के उत्तरी पर्वतीय क्षेत्रों को पृथक कर एक नए राज्य उत्तराखंड (तत्कालीन नाम उत्तरांचल ) का गठन किया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6_%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%A0%E0%A4%A8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_2000&amp;oldid=6542809</t>
+  </si>
+  <si>
+    <t>औद्योगिक (विकास एवं विनियमन) अधिनियम, 1951</t>
+  </si>
+  <si>
+    <t>औद्योगिक क्षेत्र में उच्‍चतर दर पर और खपत के आधार पर वृद्धि देश के समग्र आर्थिक विकास का एक निर्धारक है। इस संबंध में, भारत सरकार ने भारतीय उद्योग के विकास को आगे बढ़ाने और प्रोत्‍साहित करने और विश्‍व के बाजार में इसकी उत्‍पादकता तथा प्रतिस्‍पर्धात्‍मकता को बनाए रखने के लिए समय-समय पर औद्योगिक नीतियां जारी की हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%94%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%97%E0%A4%BF%E0%A4%95_(%E0%A4%B5%E0%A4%BF%E0%A4%95%E0%A4%BE%E0%A4%B8_%E0%A4%8F%E0%A4%B5%E0%A4%82_%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE%E0%A4%A8)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1951&amp;oldid=5372027</t>
+  </si>
+  <si>
+    <t>औद्योगिक विवाद अधिनियम, 1947</t>
+  </si>
+  <si>
+    <t>औद्योगिक विवाद वे विवाद हैं जो औद्योगिक संबंधों में कोई असहमति हो जाने के कारण उत्‍पन्‍न होते हैं। औद्योगिक संबंध शब्‍द से नियोजक और कर्मचारियों के बीच; कर्मचारियों के बीच तथा नियोजकों के बीच परस्‍पर संवादों के कई पहलू जुड़े हुए हैं। ऐसे संबंधों में जब भी हितों को लेकर कोई विरोध होता है तो इससे जुड़े किसी एक पक्ष में असंतोष पैदा हो जाता है और इस प्रकार औद्योगिक विवाद अथवा संघर्ष हो जाता है, यह विवाद कई रूप ले लेता है जैसे कि विरोध, हड़ताल, धरना, तालाबंदी, छंटनी, कर्मचारियों की बर्खास्‍तगी, आदि।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%94%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%97%E0%A4%BF%E0%A4%95_%E0%A4%B5%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%A6_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1947&amp;oldid=6264587</t>
+  </si>
+  <si>
+    <t>औषधि और प्रसाधन सामग्री अधिनियम, १९४०</t>
+  </si>
+  <si>
+    <t>औषधि और प्रसाधन सामग्री अधिनियम, १९४० भरत में औषधि आयात, निर्माण और वितरण को नियंत्रित करने केलिए भारतीय संसद द्वारा पारितएक अधिनियम है। इस अधिनियम का प्राथमिक उद्देश्यभारत द्वाराक्रय कीइ जने वाली औषधियों और्प्रसाधन सामग्री की सुरक्षित, प्रभावी और राज्य के मानक गुणवत्ता मापदण्डों की जाँच करना है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%94%E0%A4%B7%E0%A4%A7%E0%A4%BF_%E0%A4%94%E0%A4%B0_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A4%BE%E0%A4%A7%E0%A4%A8_%E0%A4%B8%E0%A4%BE%E0%A4%AE%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AA%E0%A5%A6&amp;oldid=4007463</t>
+  </si>
+  <si>
+    <t>कंपनी अधिनियम, 1956</t>
+  </si>
+  <si>
+    <t>कंपनी अधिनियम १९५६ वह अति महत्‍वपूर्ण विधान था जो भारत के केन्‍द्रीय सरकार को कम्‍पनी के गठन और कार्यों को विनियमित करने की शक्ति प्रदान करता था। इसे भारत की संसद द्वारा 1956 में पारित किया गया था। यह अधिनियम कम्पनियों के गठन को पंजीकृत करने तथा उनके निर्देशकों और सचिवो की जिम्मेदारी का निर्धारण करता था। यह अधिनियम भारत के संघीय सरकार द्वारा कारपोरेट मामलों के मंत्रालय, कंपनियों के रजिस्ट्रार के कार्यालय, आधिकारिक परिसमापक, सार्वजनिक न्यासी, कंपनी लॉ बोर्ड आदि के माध्यम से प्रशासित किया जाता हथा। इसमें समय-समय पर संशोधन किया गया। इस अधिनियम को समाप्त करए इसके स्थान पर कम्पनी अधिनियम, २०१३ लागू किया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1956&amp;oldid=6151386</t>
+  </si>
+  <si>
+    <t>कॉपीराइट अधिनियम १९५७</t>
+  </si>
+  <si>
+    <t>भारत में कॉपीराइट अधिकारों की रक्षा के लिए १९५७ में निर्मित विधेयक।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A5%89%E0%A4%AA%E0%A5%80%E0%A4%B0%E0%A4%BE%E0%A4%87%E0%A4%9F_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_%E0%A5%A7%E0%A5%AF%E0%A5%AB%E0%A5%AD&amp;oldid=6526414</t>
+  </si>
+  <si>
+    <t>घरेलू हिंसा से महिला संरक्षण अधिनियम, 2005</t>
+  </si>
+  <si>
+    <t>घरेलू हिंसा से महिला संरक्षण अधिनियम, 2005 भारत की संसद् द्वारा पारित एक अधिनियम है जिसका उद्देश्य घरेलू हिंसा से महिलाओं को बचाना है और पीड़ित महिलाओं को विधिक सहायता उपलब्ध कराना है। यह 26 अक्टूबर 2006 को लागू हुआ।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%98%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A5%82_%E0%A4%B9%E0%A4%BF%E0%A4%82%E0%A4%B8%E0%A4%BE_%E0%A4%B8%E0%A5%87_%E0%A4%AE%E0%A4%B9%E0%A4%BF%E0%A4%B2%E0%A4%BE_%E0%A4%B8%E0%A4%82%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_2005&amp;oldid=6328510</t>
+  </si>
+  <si>
+    <t>जम्मू और कश्मीर पुनर्गठन अधिनियम, 2019</t>
+  </si>
+  <si>
+    <t>जम्मू-कश्मीर पुनर्गठन अधिनियम २०१९ भारत की संसद का एक अधिनियम है। इसे भारत की उच्च सदन( राज्य सभा ) में गृहमन्त्री अमित शाह ने ०५ अगस्त, २०१९ को प्रस्तुत किया था। यह अधिनियम उसी दिन राज्य सभा द्वारा पारित कर दिया गया तथा अगले दिन लोक सभा ने इसे पारित कर दिया। राष्ट्रपति रामनाथ कोविंद ने ९ अगस्त २०१९ को इसे स्वीकृति दे दी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9C%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%82_%E0%A4%94%E0%A4%B0_%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE%E0%A5%80%E0%A4%B0_%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%A0%E0%A4%A8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_2019&amp;oldid=6217352</t>
+  </si>
+  <si>
+    <t>तेहत्तरवां संशोधन (भारत का संविधान)</t>
+  </si>
+  <si>
+    <t>यह अधिनियम 1992 में पारित किया गया और यह भारत में पंचायती राज व्यवस्था लागू करने के दिशा में एक बड़ा कदम था। स्थानीय स्वशासन की दृष्टि से इस संशोधन अधिनियम के द्वारा पंचायतों के गठन को संवैधानिक मान्यता प्रदान की गई है। इस संशोधन अधिनियम के द्वारा संविधान में एक नवीन भाग,भाग 9 जोड़ा गया है जो पंचायतों के विषय में है। इस भाग में अनुच्छेद 243 तथा अनुच्छेद 243क से 243ण तक नवीन अनुच्छेदों को जोड़ा गया है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A4%E0%A5%87%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0%E0%A4%B5%E0%A4%BE%E0%A4%82_%E0%A4%B8%E0%A4%82%E0%A4%B6%E0%A5%8B%E0%A4%A7%E0%A4%A8_(%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4_%E0%A4%95%E0%A4%BE_%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A4%BF%E0%A4%A7%E0%A4%BE%E0%A4%A8)&amp;oldid=6306870</t>
+  </si>
+  <si>
+    <t>दण्ड प्रक्रिया संहिता, १९७३ (भारत)</t>
+  </si>
+  <si>
+    <t>दण्ड प्रक्रिया संहिता, १९७३ (Code of Criminal Procedure, 1973) भारत में आपराधिक कानून के क्रियान्यवन के लिये निर्मित दण्ड प्रक्रिया थी। यह सन् १९७३ में पारित हुआ तथा १ अप्रैल १९७४ से लागू हुआ था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A6%E0%A4%A3%E0%A5%8D%E0%A4%A1_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A4%BE_%E0%A4%B8%E0%A4%82%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A4%BE,_%E0%A5%A7%E0%A5%AF%E0%A5%AD%E0%A5%A9_(%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4)&amp;oldid=6451205</t>
+  </si>
+  <si>
+    <t>दहेज प्रतिबंध अधिनियम, १९६१</t>
+  </si>
+  <si>
+    <t>दहेज का मतलब है कोई सम्पति या बहुमूल्य प्रतिभूति देना या देने के लिए प्रत्यक्ष या परोक्ष रूप सेः</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A6%E0%A4%B9%E0%A5%87%E0%A4%9C_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A4%BF%E0%A4%AC%E0%A4%82%E0%A4%A7_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AC%E0%A5%A7&amp;oldid=6251521</t>
+  </si>
+  <si>
+    <t>देशी प्रेस अधिनियम</t>
+  </si>
+  <si>
+    <t>अंग्रेज सरकार द्वारा भारत में सन् 1878 में देशी प्रेस अधिनियम (Vernacular Press Act) पारित किया गया ताकि भारतीय भाषाओं के पत्र-पत्रिकाओं पर और कड़ा नियंत्रण रखा जा सके। उस समय लॉर्ड लिट्टन भारत का वाइसराय था। इस अधिनियम में पत्र-पत्रिकाओं में ऐसी सामग्री छापने पर कड़ी कार्यवाही का प्रावधान था जिससे जनता में ब्रिटिश शासन के विरुद्ध असंतोष पनपने की सम्भावना हो। वस्तुतः यह कानून भाषाई समाचार-पत्रों को दबाने के लिए लाया गया था। देशी प्रेस अधिनियम पारित होने के अगले दिन ही कोलकाता से बंगला में प्रकाशित अमृत बाजार पत्रिका ने अपने को 'अंग्रेजी दैनिक' पत्र बना दिया। इसके सम्पादक शिषिर कुमार घोष थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A5%80_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=6471739</t>
+  </si>
+  <si>
+    <t>पूजा स्थल (विशेष प्रावधान) अधिनियम, 1991</t>
+  </si>
+  <si>
+    <t>प्लेसेज़ ऑफ़ वर्शिप (स्पेशल प्रोविज़न) एक्ट, 1991 या उपासना स्‍थल (विशेष उपबंध) अधिनियम, 1991 भारत की संसद का एक अधिनियम है। यह केंद्रीय कानून 18 सितंबर, 1991 को पारित किया गया था। यह 15 अगस्त 1947 तक के अस्तित्व में आए हुए किसी भी धर्म के पूजा स्थल को एक आस्था से दूसरे धर्म में परिवर्तित करने पर और किसी भी स्मारक के धार्मिक आधार पर रखरखाव पर रोक लगाता है। मान्यता प्राप्त प्राचीन स्मारकों पर धाराएं लागू नहीं होंगी। यह अधिनियम उत्तर प्रदेश राज्य के अयोध्या में स्थित राम जन्म भूमि- बाबरी मस्जिद और उक्त स्थान या पूजा स्थल से संबंधित किसी भी वाद, अपील या अन्य कार्यवाही के लिए लागू नहीं होता है। इस अधिनियम ने स्पष्ट रूप से अयोध्या विवाद से संबंधित घटनाओं को वापस करने की अक्षमता को स्वीकार किया। बाबरी संरचना को ध्वस्त करने से पहले 1991 में पी॰ वी॰ नरसिम्हा राव द्वारा एक कानून लाया गया था। यह अधिनियम जम्मू और कश्मीर राज्य को छोड़कर पूरे भारत में फैला हुआ है। राज्य के लिए लागू होने वाले किसी भी कानून को वहां की विधानसभा द्वारा अनुमोदित किया जाना चाहिए।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A5%82%E0%A4%9C%E0%A4%BE_%E0%A4%B8%E0%A5%8D%E0%A4%A5%E0%A4%B2_(%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%87%E0%A4%B7_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%B5%E0%A4%A7%E0%A4%BE%E0%A4%A8)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1991&amp;oldid=5833268</t>
+  </si>
+  <si>
+    <t>बागान श्रम अधिनियम, 1951</t>
+  </si>
+  <si>
+    <t>बागान श्रम अधिनियम, 1951 बागान श्रमिकों के कल्‍याण की व्‍यवस्‍था करता है और बागानों में कार्य परिस्थितियों को विनियमित करता है। अधिनियम के अनुसार बागान शब्‍द का अर्थ है कोई भी बागान, जिसके लिए यह अधिनियम चाहे पूर्ण रूप से या आंशिक रूप से प्रयोज्‍य होता है और इसमें कार्यालय, अस्‍पताल, दवाखाना, स्‍कूल और अन्‍य कोई परिसर ऐसे बागानों में संबंधित किसी प्रयोजन के लिए प्रयुक्‍त होता है, शामिल हैं परन्‍तु इसमें परिसर में कोई फैक्‍टरी शामिल नहीं होती है, जिसके लिए फैक्‍टरी अधिनियम 1948 के प्रावधान प्रयोज्‍य होते हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AC%E0%A4%BE%E0%A4%97%E0%A4%BE%E0%A4%A8_%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1951&amp;oldid=4776898</t>
+  </si>
+  <si>
+    <t>बेनामी लेनदेन (निषेध) अधिनियम</t>
+  </si>
+  <si>
+    <t>बेनामी लेनदेन (निषेध) अधिनियम (Benami Transactions (Prohibition) Act) भारतीय संसद द्वारा पारित एक अधिनियम है जो बेनामी लेनदेन का निषेध करता है। यह पहली बार १९८८ में पारित हुआ तथा २०१६ में इसमें संशोधन किया गया। संशोधित कानून ०१ नवम्बर, २०१६ से लागू हो गया। संशोधित बिल में बेनामी संपत्‍तियों को जब्‍त करने और उन्‍हें सील करने का अधिकार है। साथ ही, जुर्माने के साथ कैद का भी प्रावधान है। भारत में काले धन की बढ़ती समस्‍या को खत्‍म करने की दिशा में यह एक और कदम है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AC%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AE%E0%A5%80_%E0%A4%B2%E0%A5%87%E0%A4%A8%E0%A4%A6%E0%A5%87%E0%A4%A8_(%E0%A4%A8%E0%A4%BF%E0%A4%B7%E0%A5%87%E0%A4%A7)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=6545721</t>
+  </si>
+  <si>
+    <t>भारतीय आयकर अधिनियम, १९६१</t>
+  </si>
+  <si>
+    <t>आयकर अधिनियम, 1961 भारत में आयकर निर्धारण का प्रमुख कानून है। यह अधिनियम 1 अप्रैल, 1962 से प्रभाव में आया। इस अधिनियम में कुल 298 धाराएं तथा XIV अनुसूचियां शामिल हैं। संसद द्वारा पारित वित्त अधिनियम द्वारा इसमें सम्वर्धन और विलोपन के साथ प्</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%86%E0%A4%AF%E0%A4%95%E0%A4%B0_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AC%E0%A5%A7&amp;oldid=6607907</t>
+  </si>
+  <si>
+    <t>भारतीय भागीदारी अधिनियम 1932</t>
+  </si>
+  <si>
+    <t>भारतीय भागीदारी अधिनियम या 'भारतीय साझेदारी अधिनियम' ( Indian Partnership Act, 1932) भारत की संसद द्वारा १९३२ में पारित एक अधिनियम है जो सझेदारी फर्मों का नियमन करती है। इसके पारित होने के पहले सहभागिता भारतीय अनुबन्ध अधिनियम १८७२ की कुछ धाराओं के द्वारा शासित थी। यह अधिनियम निगम कार्य मंत्रालय के द्वारा अधिशासित है। साझेदारी अधिनियम के अंतगत साझेदारी</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%AD%E0%A4%BE%E0%A4%97%E0%A5%80%E0%A4%A6%E0%A4%BE%E0%A4%B0%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_1932&amp;oldid=6200902</t>
+  </si>
+  <si>
+    <t>भारतीय संविदा अधिनियम १८७२</t>
+  </si>
+  <si>
+    <t>भारतीय संविदा अधिनियम, १८७२ (Indian Contract Act, 1872) भारत का मुख्य संविदा कानून है। यह अधिनियम भारत में अंग्रेजी शासन के समय पारित हुआ था। यह 'इंग्लिश कॉमन ला' पर आधारित है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A4%BE_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_%E0%A5%A7%E0%A5%AE%E0%A5%AD%E0%A5%A8&amp;oldid=5713421</t>
   </si>
   <si>
     <t>भारतीय साक्ष्य अधिनियम, 1872</t>
   </si>
   <si>
-    <t>Indian Evidence Act, 1872</t>
-  </si>
-  <si>
-    <t>Erstwhile law of India</t>
-  </si>
-  <si>
-    <t>ब्रिटिश राज; भारत</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q1166132</t>
-  </si>
-  <si>
-    <t>भारतीय दंड संहिता</t>
-  </si>
-  <si>
-    <t>Indian Penal Code</t>
-  </si>
-  <si>
-    <t>Erstwhile Penal code of Republic of India</t>
-  </si>
-  <si>
-    <t>भारत; ब्रिटिश राज</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3519479</t>
-  </si>
-  <si>
-    <t>सूचना प्रौद्योगिकी अधिनियम, 2000</t>
-  </si>
-  <si>
-    <t>Information Technology Act, 2000</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3522823</t>
-  </si>
-  <si>
-    <t>परक्राम्य लिखत अधिनियम, 1881</t>
-  </si>
-  <si>
-    <t>Negotiable Instruments Act, 1881</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q6987432</t>
-  </si>
-  <si>
-    <t>सूचना का अधिकार अधिनियम, 2005</t>
-  </si>
-  <si>
-    <t>Right to Information Act, 2005</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2725604</t>
-  </si>
-  <si>
-    <t>विशेष विवाह अधिनियम, 1954</t>
-  </si>
-  <si>
-    <t>Special Marriage Act, 1954</t>
-  </si>
-  <si>
-    <t>Act of the Parliament of India for inter-religious and inter-faith marriage</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2812734</t>
-  </si>
-  <si>
-    <t>वन्यजीव संरक्षण अधिनियम, 1972</t>
-  </si>
-  <si>
-    <t>Wild Life (Protection) Act, 1972</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3249509</t>
+    <t>भारतीय साक्ष्य अधिनियम (Indian Evidence Act) मूल रूप से 1872 में ब्रिटिश संसद द्वारा पारित किया गया था। भारतीय साक्ष्य अधिनियम में 11 अध्याय और 167 धाराएँ हैं। यह तीन भागों में विभक्त है। इस अधिनियम ने बनने के बाद से 125 से अधिक वर्षों की अवधि के दौरान समय-समय पर कुछ संशोधन को छोड़कर अपने मूल रूप को बरकरार रखा है। यह अदालत की सभी न्यायिक कार्यवाहियों पर लागू होता है ( कोर्ट मार्शल सहित)। हालांकि, यह शपथ-पत्र और मध्‍यस्‍थता पर लागू नहीं होता है|</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%B8%E0%A4%BE%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1872&amp;oldid=6208493</t>
+  </si>
+  <si>
+    <t>भूमि अधिग्रहण अधिनियम, १८९४</t>
+  </si>
+  <si>
+    <t>भूमि अधिग्रहण अधिनियम, १८९४ ( अंग्रेज़ी : The Land Acquisition Act of 1894 ) भारत और पाकिस्तान दोनों का एक कानून है, जिसका उपयोग करके सरकारें निजी भूमि का अधिग्रहण कर सकतीं हैं। इसके लिये सरकार द्वारा भूमि मालिकों को क्षतिपूर्ति (मुआवजा) देना आवश्यक है। यह मुआवजा राशि भूमि के सर्कल रेट पर निर्भर करता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A5%82%E0%A4%AE%E0%A4%BF_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B9%E0%A4%A3_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AE%E0%A5%AF%E0%A5%AA&amp;oldid=6270387</t>
+  </si>
+  <si>
+    <t>राष्ट्रीय जाँच एजेंसी विधेयक</t>
+  </si>
+  <si>
+    <t>राष्ट्रीय जांच एजेंसी विधेयक (एनआईए विधेयक), भारत सरकार का एक कानून है जो आतंकवाद से लड़ने के निमित्त बनाया गया था। यह दिसम्बर, २००८, में भारतीय लोकसभा में पारित हुआ था। इस कानून में कई कड़े प्रावधान देने की बात कही गई।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%AF_%E0%A4%9C%E0%A4%BE%E0%A4%81%E0%A4%9A_%E0%A4%8F%E0%A4%9C%E0%A5%87%E0%A4%82%E0%A4%B8%E0%A5%80_%E0%A4%B5%E0%A4%BF%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95&amp;oldid=4791573</t>
+  </si>
+  <si>
+    <t>राष्‍ट्रीय खाद्य सुरक्षा अधिनियम</t>
+  </si>
+  <si>
+    <t>राष्‍ट्रीय खाद्य सुरक्षा अधिनियम-2013 भारत सरकार द्वारा अधिसूचित एक कानून है जिसके माध्यम से भारत सरकार का उद्देश्य यह सुनिश्चित करना है कि देश में जनसाधारण को खाद्यान्न उपलब्ध हो सके।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E2%80%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF_%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%BE_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=6270966</t>
+  </si>
+  <si>
+    <t>राष्‍ट्रीय राजमार्ग अधिनियम, 1956</t>
+  </si>
+  <si>
+    <t>राष्‍ट्रीय राजमार्ग अधिनियम, 1956 राष्‍ट्रीय राजमार्ग के विकास और प्रबंधन से संबंधित विषयों पर कार्य करता है। इसके अन्‍य मुख्‍य कार्य निम्‍नलिखित हैं :-</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E2%80%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%AF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%AE%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%97_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1956&amp;oldid=6194698</t>
+  </si>
+  <si>
+    <t>लिंग चयन प्रतिषेध अधिनियम, 1994</t>
+  </si>
+  <si>
+    <t>पूर्व गर्भाधान और प्रसव पूर्व निदान तकनीक (PCPNDT) अधिनियम, 1994 भारत में कन्या भ्रूण हत्या और गिरते लिंगानुपात को रोकने के लिए भारत की संसद द्वारा पारित एक संघीय कानून है। इस अधिनियम से प्रसव पूर्व लिंग निर्धारण पर प्रतिबंध लगा दिया गया है। प्री-नेटल डायग्नोस्टिक टेक्निक ‘पीएनडीटी’ एक्ट 1996, के तहत जन्म से पूर्व शिशु के लिंग की जांच पर पाबंदी है। ऐसे में अल्ट्रासाउंड या अल्ट्रासोनोग्राफी कराने वाले जोड़े या करने वाले डाक्टर, लैब कर्मी को तीन से पांच साल सजा और 10 से 50 हजार जुर्माने की सजा का प्रावधान है। प्रत्येक आनुवांशिक परामर्श केंद्र, आनुवांशिक प्रयोगशाला या आनुवांशिक क्लिनिक परामर्श देने या प्रसव पूर्व निदान तकनीकों का संचालन करने में लगे हुए हैं, जैसे कि गर्भाधान से पहले और बाद में लिंग चयन की संभावनाओं के साथ इन विट्रो फर्टिलाइज़ेशन (आईवीएफ) पीसीसीपीटी अधिनियम के दायरे में आता है और इस पर प्रतिबंध है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B2%E0%A4%BF%E0%A4%82%E0%A4%97_%E0%A4%9A%E0%A4%AF%E0%A4%A8_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A4%BF%E0%A4%B7%E0%A5%87%E0%A4%A7_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1994&amp;oldid=4955018</t>
+  </si>
+  <si>
+    <t>लोक सेवा गारंटी अधिनियम २०१० (म प्र)</t>
+  </si>
+  <si>
+    <t>लोक सेवा गारंटी अधिनियम २०१० भारत के मध्य प्रदेश राज्य द्वारा पारित एक विधेयक है। इसके अनुसार लोक सेवकों को तय समयसीमा में काम को पूरा करना होगा और ऐसा न होने पर जवाबदेही तय कर उन पर 500 से 5000 रुपये तक का जुर्माना लगाया जाएगा।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B2%E0%A5%8B%E0%A4%95_%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE_%E0%A4%97%E0%A4%BE%E0%A4%B0%E0%A4%82%E0%A4%9F%E0%A5%80_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_%E0%A5%A8%E0%A5%A6%E0%A5%A7%E0%A5%A6_(%E0%A4%AE_%E0%A4%AA%E0%A5%8D%E0%A4%B0)&amp;oldid=6245412</t>
+  </si>
+  <si>
+    <t>वित्त अधिनियम (भारत)</t>
+  </si>
+  <si>
+    <t>वित्त अधिनियम (Finance Act) भारत का महत्वपूर्ण अधिनियम है। इस अधिनियम के द्वारा भारत सरकार प्रत्येक वित्त वर्ष के आरम्भ में वित्तीय प्रस्ताव रखती है। यह अधिनियम भारत के सभी राज्यों एवं केन्द्र शाशित प्रदेशों पर भी लागू होता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%A4%E0%A5%8D%E0%A4%A4_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_(%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4)&amp;oldid=6200450</t>
+  </si>
+  <si>
+    <t>विदेशी कारोबार (विकास और विनियम) अधिनियम, 1992</t>
+  </si>
+  <si>
+    <t>भारत में विदेशी कारोबार से संबंधित मुख्‍य विधान विदेशी कारोबार (विकास और विनियम) अधिनियम, 1992 है। इस अधिनियम में देश में होने वाले आयात द्वारा विदेशी कारोबार के विकास और विनियमन की सुविधा प्रदान की गई है और यह भारत से निर्यात तथा इससे जुड़े या आकस्मिक मामलों का भी विकास तथा विनियमन करता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A5%80_%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%8B%E0%A4%AC%E0%A4%BE%E0%A4%B0_(%E0%A4%B5%E0%A4%BF%E0%A4%95%E0%A4%BE%E0%A4%B8_%E0%A4%94%E0%A4%B0_%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE)_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_1992&amp;oldid=4796334</t>
+  </si>
+  <si>
+    <t>विदेशी मुद्रा विनियमन अधिनियम (फेरा), 1973</t>
+  </si>
+  <si>
+    <t>जब कोई व्‍यापारी उद्यम अन्‍य देशों से वस्‍तुओं का आयात करता है, उन्‍हें अपने उत्‍पाद निर्यात करता है अथवा विदेशों में निवेश करता है तो वह विदेशी मुद्रा का लेन देन करता है। विदेशी एक्‍सचेंज का अर्थ है विदेशी मुद्रा तथा इसमें निम्‍न शामिल हैं :- (i) किसी विदेशी मुद्रा में संदेय जमा राशियां; (ii) ड्राफ्ट ( हुंडिया ), यात्री चैक , ऋणपत्र या विनिमय हुंडियां जो भारतीय मुद्रा में व्‍यक्‍त या आ‍हरित हो किन्‍तु किसी विदेशी मुद्रा में संदेय हो; तथा (iii) ड्राफ्ट, यात्री चैक, ऋण पत्र या विनिमय हुंडियां जो भारत से बाहर बैंकों, संस्‍थाओं या व्‍यक्तियों द्वारा आहरित हो किन्‍तु भारतीय मुद्रा में संदेय हों।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A5%80_%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%BE_%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE%E0%A4%A8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_(%E0%A4%AB%E0%A5%87%E0%A4%B0%E0%A4%BE),_1973&amp;oldid=5214216</t>
+  </si>
+  <si>
+    <t>विदेशी विनियम प्रबंदन अधिनियम, १९९९</t>
+  </si>
+  <si>
+    <t>विदेशी विनियम प्रबंधन अधिनियम, १९९९ | इसे फेमा के नाम से जाना जाता हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A5%80_%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A4%A8_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AF%E0%A5%AF&amp;oldid=3971284</t>
+  </si>
+  <si>
+    <t>विशेष न्यायालय विधेयक (मप्र)</t>
+  </si>
+  <si>
+    <t>विशेष न्यायालय विधेयक मध्य प्रदेश विधान सभा में अभी हाल में ही (अप्रैल २०११) पारित विधेयक है। इसमें भ्रष्टाचार में लिप्त नेताओं और सरकारी मुलाजिमों के खिलाफ प्रभावी कार्रवाई के लिए विशेष अदालतें गठित करने का प्रावधान है। इसमें काली कमाई से जुटाई संपत्ति राजसात करने और सजा का भी प्रावधान है। इसके दायरे में पंच, पार्षद से लेकर मुख्यमंत्री और भृत्य से लेकर मुख्य सचिव तक सभी लोकसेवक आएंगे। विशेष अदालतों के फैसले को उच्च न्यायालय में चुनौती दी जा सकेगी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%87%E0%A4%B7_%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%AF%E0%A4%BE%E0%A4%B2%E0%A4%AF_%E0%A4%B5%E0%A4%BF%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95_(%E0%A4%AE%E0%A4%AA%E0%A5%8D%E0%A4%B0)&amp;oldid=4796872</t>
+  </si>
+  <si>
+    <t>विशेष विवाह अधिनियम</t>
+  </si>
+  <si>
+    <t>विशेष विवाह अधिनियम, 1954 भारत की संसद् का एक अधिनियम है जो भारत के लोगों और विदेशी देशों में सभी भारतीय नागरिकों के लिए विवाह का विशेष रूप प्रदान करता है, भले ही किसी भी पार्टी के बाद धर्म या विश्वास के बावजूद। यह अधिनियम 19वीं शताब्दी के उत्तरार्ध में प्रस्तावित कानून के एक टुकड़े से हुआ था। विशेष विवाह अधिनियम के तहत गमृभीर विवाह व्यक्तिगत कानूनों द्वारा शासित नहीं होते हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%87%E0%A4%B7_%E0%A4%B5%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B9_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=5834955</t>
+  </si>
+  <si>
+    <t>शत्रु सम्पत्ति अधिनियम, १९६८</t>
+  </si>
+  <si>
+    <t>शत्रु सम्पत्ति अधिनियम 1968 भारतीय संसद द्वारा पारित एक अधिनियम है जिसके अनुसार शत्रु सम्पत्ति पर भारत सरकार का अधिकार होगा। पाकिस्तान से 1965 में हुए युद्ध के बाद 1968 में शत्रु संपत्ति (संरक्षण एवं पंजीकरण) अधिनियम पारित हुआ था। इस अधिनियम के अनुसार जो लोग बंटवारे या 1965 में और 1971 की लड़ाई के बाद पाकिस्तान चले गए और वहां की नागरिकता ले ली थी, उनकी सारी अचल संपत्ति 'शत्रु संपत्ति' घोषित कर दी गई। उसके बाद पहली बार उन भारतीय नागरिकों को संपत्ति के आधार पर 'शत्रु' की श्रेणी में रखा गया, जिनके पूर्वज किसी ‘शत्रु’ राष्ट्र के नागरिक रहे हों। यह कानून केवल उनकी संपत्ति को लेकर है और इससे उनकी भारतीय नागरिकता पर इसका कोई असर नहीं पड़ता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B6%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%81_%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%BF_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE,_%E0%A5%A7%E0%A5%AF%E0%A5%AC%E0%A5%AE&amp;oldid=4798158</t>
+  </si>
+  <si>
+    <t>शहरी भूमि सीलिंग अधिनियम</t>
+  </si>
+  <si>
+    <t>शहरी भूमि सीलिंग अधिनियम भारत में १९७६ में पारित किया गया था। यह अधिनियम शहरी विकास पर एक बड़ी बाधा है, अतः कई राज्यों ने इसे हटा दिया है, जैसे कि गुजरात और महाराष्ट्र | हालांकि, वहाँ अभी भी भवनों के लिए भूमि की निकासी के लिए आवश्यक प्रक्रिया में काफी भ्रम की स्थिति है, क्योंकि कानून के निरस्त होने का जमीनी तोर पर ज्यादा प्रभाव नहीं पड़ा है। महाराष्ट्र सरकार ने आम लोगों के लिए कम लागत के आवास उपलब्ध कराने के लिए इस अधिनियम के प्रावधानों के तहत जमीन के बड़े हिस्सों को खरीदा है। निरस्त की पूर्व शर्त के अनुसार राज्य सरकारों को जवाहर लाल नेहरू राष्ट्रीय शहरी नवीकरण मिशन (जेएनएनयूआरएम) के तहत अनुदान करना था, जिसका इस्तेमाल प्रमुख बुनियादी विकास परियोजनाओं के लिए होगा।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B6%E0%A4%B9%E0%A4%B0%E0%A5%80_%E0%A4%AD%E0%A5%82%E0%A4%AE%E0%A4%BF_%E0%A4%B8%E0%A5%80%E0%A4%B2%E0%A4%BF%E0%A4%82%E0%A4%97_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE&amp;oldid=3971286</t>
+  </si>
+  <si>
+    <t>संविदा श्रम (विनियमन एवं उन्‍मूलन), अधिनियम 1970</t>
+  </si>
+  <si>
+    <t>संविदा श्रम (विनियमन एवं उन्‍मूलन), अधिनियम का उद्देश्‍य संविदा श्रम के नियोजन को विनियमित करना है ताकि इसे काम की स्थितियों और कुछ अन्‍य लाभों के संदर्भ में सीधे नियोजन श्रम-शक्ति के समकक्ष लाया जा सके। संविदा श्रम का अर्थ है प्रयोक्‍ता उद्यमों के लिए ठेकेदार द्वारा काम में लगाए गए कामगार। ये कामगार आमतौर पर कृषि प्रचालनों, बागानी, निर्माण उद्योग, पत्तन और गोदी ऑयल फील्‍ड कारखानों, रेलवे, नौवहन, एयरलाइनों, सड़क परिवहन इत्‍यादि में लगाए जाते हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A4%BE_%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE_(%E0%A4%B5%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE%E0%A4%A8_%E0%A4%8F%E0%A4%B5%E0%A4%82_%E0%A4%89%E0%A4%A8%E0%A5%8D%E2%80%8D%E0%A4%AE%E0%A5%82%E0%A4%B2%E0%A4%A8),_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_1970&amp;oldid=5532745</t>
+  </si>
+  <si>
+    <t>सनदी लेखाकार अधिनियम 1949</t>
+  </si>
+  <si>
+    <t>सनदी लेखाकार अधिनियम, 1949 भारत में लेखांकन के पेशे को विनियमित करने के लिए भारत की संसद द्वारा पारित कानून है। यह भारतीय संविधान सभा द्वारा अधिनियमित किया गया था जो की १९४९ में भारत की अनंतिम संसद के रूप में कार्य कर रही थी। इस अधिनियम के तहत भारत में चार्टर्ड एकाउंटेंट्स को शिक्षित, विनियमित और पंजीकृत करने के लिए भारतीय सनदी लेखाकार संस्थान को स्थापित किया गया था। he Institute of Chartered Accountants of India (ICAI) is a statutory body established under the Chartered Accountants Act, 1949 (Act No. XXXVIII of 1949) for the regulation of the profession of Chartered Accountants in India. During its 61 years of existence, ICAI has achieved recognition as a premier accounting body not only in the country but also globally, for its contribution in the fields of education, professional development, maintenance of high accounting, auditing and ethical standards.ICAI now is the second largest accounting body in the whole world.</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%A8%E0%A4%A6%E0%A5%80_%E0%A4%B2%E0%A5%87%E0%A4%96%E0%A4%BE%E0%A4%95%E0%A4%BE%E0%A4%B0_%E0%A4%85%E0%A4%A7%E0%A4%BF%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A4%AE_1949&amp;oldid=3971291</t>
+  </si>
+  <si>
+    <t>सिविल प्रक्रिया संहिता, १९०८</t>
+  </si>
+  <si>
+    <t>सिविल प्रक्रिया संहिता, १९०८ (The Code of Civil Procedure, 1908) भारत का सिविल प्रक्रिया सम्बन्धी कानून है। यह पहली बार १८५९ में लागू हुआ था। इसे व्यवहार प्रक्रिया संहिता भी कहते हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%BF%E0%A4%B5%E0%A4%BF%E0%A4%B2_%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A4%BE_%E0%A4%B8%E0%A4%82%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A4%BE,_%E0%A5%A7%E0%A5%AF%E0%A5%A6%E0%A5%AE&amp;oldid=6429512</t>
   </si>
 </sst>
 </file>
@@ -214,10 +496,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,18 +843,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,238 +861,537 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" ht="409" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="7" ht="240" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="8" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="10" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="11" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="12" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="13" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="14" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="15" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="16" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="18" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="C18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" ht="176" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" ht="128" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" ht="160" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
